--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:47</t>
+    <t xml:space="preserve">2026-09-09 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:53</t>
+    <t xml:space="preserve">2026-09-18 10:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -995,7 +995,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1004,12 +1004,12 @@
         <v>27</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>28.63</v>
+        <v>24.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1018,12 +1018,12 @@
         <v>28</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>68.4</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1032,12 +1032,12 @@
         <v>29</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>96.51</v>
+        <v>95.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -1046,12 +1046,12 @@
         <v>27</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>21.19</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1060,12 +1060,12 @@
         <v>28</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>66.33</v>
+        <v>68.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -1074,12 +1074,12 @@
         <v>29</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>96.35</v>
+        <v>96.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
@@ -1088,12 +1088,12 @@
         <v>27</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>24.52</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
@@ -1102,12 +1102,12 @@
         <v>28</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>65.88</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
@@ -1116,12 +1116,12 @@
         <v>29</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95.49</v>
+        <v>96.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
@@ -1130,12 +1130,12 @@
         <v>30</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>95</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -1144,12 +1144,12 @@
         <v>31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>98.74</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -1158,12 +1158,12 @@
         <v>30</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>94.93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -1172,12 +1172,12 @@
         <v>31</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>98.35</v>
+        <v>98.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
@@ -1186,12 +1186,12 @@
         <v>30</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>94.33</v>
+        <v>94.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
@@ -1200,12 +1200,12 @@
         <v>31</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>96.5</v>
+        <v>98.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -1214,12 +1214,12 @@
         <v>32</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>89.11</v>
+        <v>90.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
@@ -1228,12 +1228,12 @@
         <v>33</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>86.32</v>
+        <v>87.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
@@ -1242,12 +1242,12 @@
         <v>32</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>91.25</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
@@ -1256,12 +1256,12 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>87.96</v>
+        <v>86.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
@@ -1270,12 +1270,12 @@
         <v>32</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>90.24</v>
+        <v>91.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
@@ -1284,7 +1284,7 @@
         <v>33</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>87.41</v>
+        <v>87.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:43</t>
+    <t xml:space="preserve">2026-09-23 16:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_biobio.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:27</t>
+    <t xml:space="preserve">2026-10-05 06:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
